--- a/excel-files/CALOOCAN/CAYETANO ARELLANO ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/CAYETANO ARELLANO ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="226" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3812BC89-411A-42F9-958E-B1A8B4A420D6}"/>
+  <xr:revisionPtr revIDLastSave="280" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2676DE74-5E43-4C95-AE26-AE6A63E4DF2B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -4560,12 +4560,15 @@
     <protectedRange sqref="F1:F50" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E41:E49 E2:E6 E8:E12" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E41:E49" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F2:F6 F8:F12" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29 E31:E39" xr:uid="{BE3A256E-65C6-4CA8-82EC-5AB8598803C8}">
+      <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8705,12 +8708,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X53:X61 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L53:L61 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R53:R61 R14:R21 R5:R12 F43:F51 F33:F41 F23:F31 F53:F61 F5:F12 F14:F21" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X53:X61" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M62 Y14:Y62 S4:S62 G5:G12 M5:M12 Y5:Y12 G23:G31 G43:G51 G33:G41 G53:G61 G14:G21" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51" xr:uid="{59ADCCAC-4847-4913-B11D-22ECBDE30023}">
+      <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13094,12 +13100,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 Y55:Y65 M55:M65 G55:G65 S55:S65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L55:L65 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F55:F65 F3:F10 F12:F19 X55:X65 R55:R65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X55:X65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025  ,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53" xr:uid="{13B72FDF-E9EE-4E4B-A90F-4D69861DA36C}">
+      <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-files/CALOOCAN/CAYETANO ARELLANO ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/CAYETANO ARELLANO ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="280" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2676DE74-5E43-4C95-AE26-AE6A63E4DF2B}"/>
+  <xr:revisionPtr revIDLastSave="281" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{756C1108-0CE1-42CA-AF00-BDFAE4AA8B13}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -2938,8 +2938,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H50" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
-  <autoFilter ref="A1:H50" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H49" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+  <autoFilter ref="A1:H49" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
     <tableColumn id="2" xr3:uid="{56826189-DC15-4CA2-B5A0-8F4CEC09DDAB}" name="SUBJECTS"/>
@@ -3383,7 +3383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -4496,16 +4496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-    </row>
+    <row r="50" spans="1:8" ht="15"/>
     <row r="51" spans="1:8" ht="15"/>
     <row r="52" spans="1:8" ht="15"/>
     <row r="53" spans="1:8" ht="15"/>
@@ -4553,22 +4544,18 @@
     <row r="95" ht="15"/>
     <row r="96" ht="15"/>
     <row r="97" ht="15"/>
-    <row r="98" ht="15"/>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C1:E50" name="Textbooks"/>
-    <protectedRange sqref="F1:F50" name="SOURCE"/>
+    <protectedRange sqref="C1:E49" name="Textbooks"/>
+    <protectedRange sqref="F1:F49" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E41:E49" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E41:E49 E2:E6 E8:E12 E14:E19 E21:E29 E31:E39" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F2:F6 F8:F12" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29 E31:E39" xr:uid="{BE3A256E-65C6-4CA8-82EC-5AB8598803C8}">
-      <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8708,15 +8695,12 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X53:X61" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X53:X61 F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M62 Y14:Y62 S4:S62 G5:G12 M5:M12 Y5:Y12 G23:G31 G43:G51 G33:G41 G53:G61 G14:G21" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51" xr:uid="{59ADCCAC-4847-4913-B11D-22ECBDE30023}">
-      <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13100,14 +13084,11 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 Y55:Y65 M55:M65 G55:G65 S55:S65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X55:X65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025  ,2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53" xr:uid="{13B72FDF-E9EE-4E4B-A90F-4D69861DA36C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X55:X65 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
   </dataValidations>
